--- a/panchang-data/NewDelhi2026.xlsx
+++ b/panchang-data/NewDelhi2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5402">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16231,6 +16231,9 @@
   </si>
   <si>
     <t>121°05'03.00</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16720,7 +16723,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16806,7 +16809,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16892,7 +16895,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16978,7 +16981,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17064,7 +17067,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17150,7 +17153,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17236,7 +17239,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17322,7 +17325,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17408,7 +17411,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17494,7 +17497,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17580,7 +17583,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17666,7 +17669,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17752,7 +17755,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17838,7 +17841,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17924,7 +17927,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18010,7 +18013,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18096,7 +18099,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18182,7 +18185,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18268,7 +18271,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18354,7 +18357,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18440,7 +18443,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18526,7 +18529,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18612,7 +18615,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18698,7 +18701,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18784,7 +18787,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18870,7 +18873,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18956,7 +18959,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19042,7 +19045,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19128,7 +19131,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19214,7 +19217,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19300,7 +19303,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19386,7 +19389,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19472,7 +19475,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19558,7 +19561,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19644,7 +19647,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19730,7 +19733,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19816,7 +19819,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19902,7 +19905,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19988,7 +19991,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20074,7 +20077,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20160,7 +20163,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20246,7 +20249,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20332,7 +20335,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20418,7 +20421,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20504,7 +20507,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20590,7 +20593,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20676,7 +20679,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20762,7 +20765,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20848,7 +20851,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20934,7 +20937,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21020,7 +21023,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21106,7 +21109,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21192,7 +21195,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21278,7 +21281,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21364,7 +21367,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21450,7 +21453,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21536,7 +21539,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21622,7 +21625,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21708,7 +21711,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21794,7 +21797,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21880,7 +21883,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21966,7 +21969,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22052,7 +22055,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22138,7 +22141,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22224,7 +22227,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22310,7 +22313,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22396,7 +22399,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22482,7 +22485,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22568,7 +22571,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22654,7 +22657,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22740,7 +22743,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22826,7 +22829,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22912,7 +22915,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22998,7 +23001,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23084,7 +23087,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23170,7 +23173,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23256,7 +23259,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23342,7 +23345,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23428,7 +23431,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23514,7 +23517,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23600,7 +23603,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23686,7 +23689,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23772,7 +23775,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23858,7 +23861,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23944,7 +23947,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24030,7 +24033,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24116,7 +24119,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24202,7 +24205,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24288,7 +24291,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24374,7 +24377,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24460,7 +24463,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24546,7 +24549,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24632,7 +24635,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24718,7 +24721,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24804,7 +24807,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24890,7 +24893,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24976,7 +24979,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25062,7 +25065,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25148,7 +25151,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25234,7 +25237,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25320,7 +25323,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25406,7 +25409,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25492,7 +25495,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25578,7 +25581,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25664,7 +25667,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25750,7 +25753,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25836,7 +25839,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25922,7 +25925,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26008,7 +26011,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26094,7 +26097,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26180,7 +26183,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26266,7 +26269,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26352,7 +26355,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26438,7 +26441,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26524,7 +26527,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26610,7 +26613,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26696,7 +26699,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26782,7 +26785,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26868,7 +26871,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26954,7 +26957,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27040,7 +27043,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1450</v>
+        <v>1873</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27126,7 +27129,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27212,7 +27215,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27298,7 +27301,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27384,7 +27387,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27470,7 +27473,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27556,7 +27559,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27642,7 +27645,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27728,7 +27731,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27814,7 +27817,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27900,7 +27903,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27986,7 +27989,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28072,7 +28075,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28158,7 +28161,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28244,7 +28247,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28330,7 +28333,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28416,7 +28419,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28502,7 +28505,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28588,7 +28591,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28674,7 +28677,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28760,7 +28763,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28846,7 +28849,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28932,7 +28935,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29018,7 +29021,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29104,7 +29107,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29190,7 +29193,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29276,7 +29279,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29362,7 +29365,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29448,7 +29451,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29534,7 +29537,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29620,7 +29623,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1873</v>
+        <v>5401</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29706,7 +29709,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29792,7 +29795,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29878,7 +29881,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29964,7 +29967,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30050,7 +30053,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30136,7 +30139,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30222,7 +30225,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30308,7 +30311,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30394,7 +30397,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30480,7 +30483,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30566,7 +30569,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30652,7 +30655,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30738,7 +30741,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30824,7 +30827,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30910,7 +30913,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2310</v>
+        <v>5401</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
